--- a/RequirementsSpecifications&PhaseWisePlanning.xlsx
+++ b/RequirementsSpecifications&PhaseWisePlanning.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A159000-620A-4EC0-9850-CB8C13359756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Design-Thinking-Session-2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B661BDA6-8B0D-451C-A131-293A990CE7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="RequirementSpecification" sheetId="1" r:id="rId1"/>
+    <sheet name="PhasePlanning" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -701,7 +706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30.75">
+    <row r="2" spans="1:5" ht="30">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -712,7 +717,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30.75">
+    <row r="3" spans="1:5" ht="30">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -724,7 +729,7 @@
       </c>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" spans="1:5" ht="106.5">
+    <row r="4" spans="1:5" ht="105">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -735,7 +740,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="91.5">
+    <row r="5" spans="1:5" ht="105">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
@@ -744,7 +749,7 @@
       </c>
       <c r="C5" s="4"/>
     </row>
-    <row r="6" spans="1:5" ht="76.5">
+    <row r="6" spans="1:5" ht="90">
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
@@ -753,7 +758,7 @@
       </c>
       <c r="C6" s="4"/>
     </row>
-    <row r="7" spans="1:5" ht="60.75">
+    <row r="7" spans="1:5" ht="60">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
@@ -764,7 +769,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="76.5">
+    <row r="8" spans="1:5" ht="75">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -773,7 +778,7 @@
       </c>
       <c r="C8" s="4"/>
     </row>
-    <row r="9" spans="1:5" ht="91.5">
+    <row r="9" spans="1:5" ht="105">
       <c r="A9" s="3" t="s">
         <v>20</v>
       </c>
